--- a/config/子种族名字替换词典.xlsx
+++ b/config/子种族名字替换词典.xlsx
@@ -32,7 +32,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="1">
+  <numFmts count="5">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
   </numFmts>
   <fonts count="1">
@@ -397,7 +401,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H99"/>
+  <dimension ref="A1:H140"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -2973,9 +2977,1075 @@
         <v>Zendikar Vampire</v>
       </c>
     </row>
+    <row r="100">
+      <c r="A100" t="str">
+        <v>半精灵</v>
+      </c>
+      <c r="B100" t="str">
+        <v>Half-Elf</v>
+      </c>
+      <c r="C100" t="str">
+        <v>PHB</v>
+      </c>
+      <c r="D100" t="str">
+        <v>变体; 水生精灵血统; 多才多艺</v>
+      </c>
+      <c r="E100" t="str">
+        <v>Variant; Aquatic Elf Descent; Skill Versatility</v>
+      </c>
+      <c r="F100" t="str">
+        <v>SCAG</v>
+      </c>
+      <c r="G100" t="str">
+        <v>变体; 水生精灵血统; 多才多艺</v>
+      </c>
+      <c r="H100" t="str">
+        <v>Variant; Aquatic Elf Descent; Skill Versatility</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="str">
+        <v>半精灵</v>
+      </c>
+      <c r="B101" t="str">
+        <v>Half-Elf</v>
+      </c>
+      <c r="C101" t="str">
+        <v>PHB</v>
+      </c>
+      <c r="D101" t="str">
+        <v>变体; 水生精灵血统; 游泳速度</v>
+      </c>
+      <c r="E101" t="str">
+        <v>Variant; Aquatic Elf Descent; Swim Speed</v>
+      </c>
+      <c r="F101" t="str">
+        <v>SCAG</v>
+      </c>
+      <c r="G101" t="str">
+        <v>变体; 水生精灵血统; 游泳速度</v>
+      </c>
+      <c r="H101" t="str">
+        <v>Variant; Aquatic Elf Descent; Swim Speed</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="str">
+        <v>半精灵</v>
+      </c>
+      <c r="B102" t="str">
+        <v>Half-Elf</v>
+      </c>
+      <c r="C102" t="str">
+        <v>PHB</v>
+      </c>
+      <c r="D102" t="str">
+        <v>变体; 卓尔血统; 卓尔魔法</v>
+      </c>
+      <c r="E102" t="str">
+        <v>Variant; Drow Descent; Drow Magic</v>
+      </c>
+      <c r="F102" t="str">
+        <v>SCAG</v>
+      </c>
+      <c r="G102" t="str">
+        <v>变体; 卓尔血统; 卓尔魔法</v>
+      </c>
+      <c r="H102" t="str">
+        <v>Variant; Drow Descent; Drow Magic</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="str">
+        <v>半精灵</v>
+      </c>
+      <c r="B103" t="str">
+        <v>Half-Elf</v>
+      </c>
+      <c r="C103" t="str">
+        <v>PHB</v>
+      </c>
+      <c r="D103" t="str">
+        <v>变体; 卓尔血统; 多才多艺</v>
+      </c>
+      <c r="E103" t="str">
+        <v>Variant; Drow Descent; Skill Versatility</v>
+      </c>
+      <c r="F103" t="str">
+        <v>SCAG</v>
+      </c>
+      <c r="G103" t="str">
+        <v>变体; 卓尔血统; 多才多艺</v>
+      </c>
+      <c r="H103" t="str">
+        <v>Variant; Drow Descent; Skill Versatility</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="str">
+        <v>半精灵</v>
+      </c>
+      <c r="B104" t="str">
+        <v>Half-Elf</v>
+      </c>
+      <c r="C104" t="str">
+        <v>PHB</v>
+      </c>
+      <c r="D104" t="str">
+        <v>变体; 月精灵或日精灵血统; 戏法</v>
+      </c>
+      <c r="E104" t="str">
+        <v>Variant; Moon Elf or Sun Elf Descent; Cantrip</v>
+      </c>
+      <c r="F104" t="str">
+        <v>SCAG</v>
+      </c>
+      <c r="G104" t="str">
+        <v>变体; 月精灵或日精灵血统; 戏法</v>
+      </c>
+      <c r="H104" t="str">
+        <v>Variant; Moon Elf or Sun Elf Descent; Cantrip</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="str">
+        <v>半精灵</v>
+      </c>
+      <c r="B105" t="str">
+        <v>Half-Elf</v>
+      </c>
+      <c r="C105" t="str">
+        <v>PHB</v>
+      </c>
+      <c r="D105" t="str">
+        <v>变体; 月精灵或日精灵血统; 精灵武器训练</v>
+      </c>
+      <c r="E105" t="str">
+        <v>Variant; Moon Elf or Sun Elf Descent; Elf Weapon Training</v>
+      </c>
+      <c r="F105" t="str">
+        <v>SCAG</v>
+      </c>
+      <c r="G105" t="str">
+        <v>变体; 月精灵或日精灵血统; 精灵武器训练</v>
+      </c>
+      <c r="H105" t="str">
+        <v>Variant; Moon Elf or Sun Elf Descent; Elf Weapon Training</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="str">
+        <v>半精灵</v>
+      </c>
+      <c r="B106" t="str">
+        <v>Half-Elf</v>
+      </c>
+      <c r="C106" t="str">
+        <v>PHB</v>
+      </c>
+      <c r="D106" t="str">
+        <v>变体; 月精灵或日精灵血统; 多才多艺</v>
+      </c>
+      <c r="E106" t="str">
+        <v>Variant; Moon Elf or Sun Elf Descent; Skill Versatility</v>
+      </c>
+      <c r="F106" t="str">
+        <v>SCAG</v>
+      </c>
+      <c r="G106" t="str">
+        <v>变体; 月精灵或日精灵血统; 多才多艺</v>
+      </c>
+      <c r="H106" t="str">
+        <v>Variant; Moon Elf or Sun Elf Descent; Skill Versatility</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="str">
+        <v>半精灵</v>
+      </c>
+      <c r="B107" t="str">
+        <v>Half-Elf</v>
+      </c>
+      <c r="C107" t="str">
+        <v>PHB</v>
+      </c>
+      <c r="D107" t="str">
+        <v>变体; 木精灵血统; 精灵武器训练</v>
+      </c>
+      <c r="E107" t="str">
+        <v>Variant; Wood Elf Descent; Elf Weapon Training</v>
+      </c>
+      <c r="F107" t="str">
+        <v>SCAG</v>
+      </c>
+      <c r="G107" t="str">
+        <v>变体; 木精灵血统; 精灵武器训练</v>
+      </c>
+      <c r="H107" t="str">
+        <v>Variant; Wood Elf Descent; Elf Weapon Training</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="str">
+        <v>半精灵</v>
+      </c>
+      <c r="B108" t="str">
+        <v>Half-Elf</v>
+      </c>
+      <c r="C108" t="str">
+        <v>PHB</v>
+      </c>
+      <c r="D108" t="str">
+        <v>变体; 木精灵血统; 轻捷步伐</v>
+      </c>
+      <c r="E108" t="str">
+        <v>Variant; Wood Elf Descent; Fleet of Foot</v>
+      </c>
+      <c r="F108" t="str">
+        <v>SCAG</v>
+      </c>
+      <c r="G108" t="str">
+        <v>变体; 木精灵血统; 轻捷步伐</v>
+      </c>
+      <c r="H108" t="str">
+        <v>Variant; Wood Elf Descent; Fleet of Foot</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="str">
+        <v>半精灵</v>
+      </c>
+      <c r="B109" t="str">
+        <v>Half-Elf</v>
+      </c>
+      <c r="C109" t="str">
+        <v>PHB</v>
+      </c>
+      <c r="D109" t="str">
+        <v>变体; 木精灵血统; 荒野隐蔽</v>
+      </c>
+      <c r="E109" t="str">
+        <v>Variant; Wood Elf Descent; Mask of the Wild</v>
+      </c>
+      <c r="F109" t="str">
+        <v>SCAG</v>
+      </c>
+      <c r="G109" t="str">
+        <v>变体; 木精灵血统; 荒野隐蔽</v>
+      </c>
+      <c r="H109" t="str">
+        <v>Variant; Wood Elf Descent; Mask of the Wild</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="str">
+        <v>半精灵</v>
+      </c>
+      <c r="B110" t="str">
+        <v>Half-Elf</v>
+      </c>
+      <c r="C110" t="str">
+        <v>PHB</v>
+      </c>
+      <c r="D110" t="str">
+        <v>变体; 木精灵血统; 多才多艺</v>
+      </c>
+      <c r="E110" t="str">
+        <v>Variant; Wood Elf Descent; Skill Versatility</v>
+      </c>
+      <c r="F110" t="str">
+        <v>SCAG</v>
+      </c>
+      <c r="G110" t="str">
+        <v>变体; 木精灵血统; 多才多艺</v>
+      </c>
+      <c r="H110" t="str">
+        <v>Variant; Wood Elf Descent; Skill Versatility</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="str">
+        <v>龙裔</v>
+      </c>
+      <c r="B111" t="str">
+        <v>Dragonborn</v>
+      </c>
+      <c r="C111" t="str">
+        <v>PHB</v>
+      </c>
+      <c r="D111" t="str">
+        <v>龙裔 (黑)</v>
+      </c>
+      <c r="E111" t="str">
+        <v>Dragonborn (Black)</v>
+      </c>
+      <c r="F111" t="str">
+        <v>PHB</v>
+      </c>
+      <c r="G111" t="str">
+        <v>龙裔 (黑)</v>
+      </c>
+      <c r="H111" t="str">
+        <v>Dragonborn (Black)</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="str">
+        <v>龙裔</v>
+      </c>
+      <c r="B112" t="str">
+        <v>Dragonborn</v>
+      </c>
+      <c r="C112" t="str">
+        <v>PHB</v>
+      </c>
+      <c r="D112" t="str">
+        <v>龙裔 (蓝)</v>
+      </c>
+      <c r="E112" t="str">
+        <v>Dragonborn (Blue)</v>
+      </c>
+      <c r="F112" t="str">
+        <v>PHB</v>
+      </c>
+      <c r="G112" t="str">
+        <v>龙裔 (蓝)</v>
+      </c>
+      <c r="H112" t="str">
+        <v>Dragonborn (Blue)</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="str">
+        <v>龙裔</v>
+      </c>
+      <c r="B113" t="str">
+        <v>Dragonborn</v>
+      </c>
+      <c r="C113" t="str">
+        <v>PHB</v>
+      </c>
+      <c r="D113" t="str">
+        <v>龙裔 (黄铜)</v>
+      </c>
+      <c r="E113" t="str">
+        <v>Dragonborn (Brass)</v>
+      </c>
+      <c r="F113" t="str">
+        <v>PHB</v>
+      </c>
+      <c r="G113" t="str">
+        <v>龙裔 (黄铜)</v>
+      </c>
+      <c r="H113" t="str">
+        <v>Dragonborn (Brass)</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="str">
+        <v>龙裔</v>
+      </c>
+      <c r="B114" t="str">
+        <v>Dragonborn</v>
+      </c>
+      <c r="C114" t="str">
+        <v>PHB</v>
+      </c>
+      <c r="D114" t="str">
+        <v>龙裔 (青铜)</v>
+      </c>
+      <c r="E114" t="str">
+        <v>Dragonborn (Bronze)</v>
+      </c>
+      <c r="F114" t="str">
+        <v>PHB</v>
+      </c>
+      <c r="G114" t="str">
+        <v>龙裔 (青铜)</v>
+      </c>
+      <c r="H114" t="str">
+        <v>Dragonborn (Bronze)</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="str">
+        <v>龙裔</v>
+      </c>
+      <c r="B115" t="str">
+        <v>Dragonborn</v>
+      </c>
+      <c r="C115" t="str">
+        <v>PHB</v>
+      </c>
+      <c r="D115" t="str">
+        <v>龙裔 (赤铜)</v>
+      </c>
+      <c r="E115" t="str">
+        <v>Dragonborn (Copper)</v>
+      </c>
+      <c r="F115" t="str">
+        <v>PHB</v>
+      </c>
+      <c r="G115" t="str">
+        <v>龙裔 (赤铜)</v>
+      </c>
+      <c r="H115" t="str">
+        <v>Dragonborn (Copper)</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="str">
+        <v>龙裔</v>
+      </c>
+      <c r="B116" t="str">
+        <v>Dragonborn</v>
+      </c>
+      <c r="C116" t="str">
+        <v>PHB</v>
+      </c>
+      <c r="D116" t="str">
+        <v>龙裔 (金)</v>
+      </c>
+      <c r="E116" t="str">
+        <v>Dragonborn (Gold)</v>
+      </c>
+      <c r="F116" t="str">
+        <v>PHB</v>
+      </c>
+      <c r="G116" t="str">
+        <v>龙裔 (金)</v>
+      </c>
+      <c r="H116" t="str">
+        <v>Dragonborn (Gold)</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="str">
+        <v>龙裔</v>
+      </c>
+      <c r="B117" t="str">
+        <v>Dragonborn</v>
+      </c>
+      <c r="C117" t="str">
+        <v>PHB</v>
+      </c>
+      <c r="D117" t="str">
+        <v>龙裔 (绿)</v>
+      </c>
+      <c r="E117" t="str">
+        <v>Dragonborn (Green)</v>
+      </c>
+      <c r="F117" t="str">
+        <v>PHB</v>
+      </c>
+      <c r="G117" t="str">
+        <v>龙裔 (绿)</v>
+      </c>
+      <c r="H117" t="str">
+        <v>Dragonborn (Green)</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="str">
+        <v>龙裔</v>
+      </c>
+      <c r="B118" t="str">
+        <v>Dragonborn</v>
+      </c>
+      <c r="C118" t="str">
+        <v>PHB</v>
+      </c>
+      <c r="D118" t="str">
+        <v>龙裔 (红)</v>
+      </c>
+      <c r="E118" t="str">
+        <v>Dragonborn (Red)</v>
+      </c>
+      <c r="F118" t="str">
+        <v>PHB</v>
+      </c>
+      <c r="G118" t="str">
+        <v>龙裔 (红)</v>
+      </c>
+      <c r="H118" t="str">
+        <v>Dragonborn (Red)</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="str">
+        <v>龙裔</v>
+      </c>
+      <c r="B119" t="str">
+        <v>Dragonborn</v>
+      </c>
+      <c r="C119" t="str">
+        <v>PHB</v>
+      </c>
+      <c r="D119" t="str">
+        <v>龙裔 (银)</v>
+      </c>
+      <c r="E119" t="str">
+        <v>Dragonborn (Silver)</v>
+      </c>
+      <c r="F119" t="str">
+        <v>PHB</v>
+      </c>
+      <c r="G119" t="str">
+        <v>龙裔 (银)</v>
+      </c>
+      <c r="H119" t="str">
+        <v>Dragonborn (Silver)</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="str">
+        <v>龙裔</v>
+      </c>
+      <c r="B120" t="str">
+        <v>Dragonborn</v>
+      </c>
+      <c r="C120" t="str">
+        <v>PHB</v>
+      </c>
+      <c r="D120" t="str">
+        <v>龙裔 (白)</v>
+      </c>
+      <c r="E120" t="str">
+        <v>Dragonborn (White)</v>
+      </c>
+      <c r="F120" t="str">
+        <v>PHB</v>
+      </c>
+      <c r="G120" t="str">
+        <v>龙裔 (白)</v>
+      </c>
+      <c r="H120" t="str">
+        <v>Dragonborn (White)</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="str">
+        <v>龙裔</v>
+      </c>
+      <c r="B121" t="str">
+        <v>Dragonborn</v>
+      </c>
+      <c r="C121" t="str">
+        <v>PHB</v>
+      </c>
+      <c r="D121" t="str">
+        <v>龙裔 (龙血裔; 黑)</v>
+      </c>
+      <c r="E121" t="str">
+        <v>Dragonborn (Draconblood; Black)</v>
+      </c>
+      <c r="F121" t="str">
+        <v>EGW</v>
+      </c>
+      <c r="G121" t="str">
+        <v>龙裔 (龙血裔; 黑)</v>
+      </c>
+      <c r="H121" t="str">
+        <v>Dragonborn (Draconblood; Black)</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="str">
+        <v>龙裔</v>
+      </c>
+      <c r="B122" t="str">
+        <v>Dragonborn</v>
+      </c>
+      <c r="C122" t="str">
+        <v>PHB</v>
+      </c>
+      <c r="D122" t="str">
+        <v>龙裔 (龙血裔; 蓝)</v>
+      </c>
+      <c r="E122" t="str">
+        <v>Dragonborn (Draconblood; Blue)</v>
+      </c>
+      <c r="F122" t="str">
+        <v>EGW</v>
+      </c>
+      <c r="G122" t="str">
+        <v>龙裔 (龙血裔; 蓝)</v>
+      </c>
+      <c r="H122" t="str">
+        <v>Dragonborn (Draconblood; Blue)</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="str">
+        <v>龙裔</v>
+      </c>
+      <c r="B123" t="str">
+        <v>Dragonborn</v>
+      </c>
+      <c r="C123" t="str">
+        <v>PHB</v>
+      </c>
+      <c r="D123" t="str">
+        <v>龙裔 (龙血裔; 黄铜)</v>
+      </c>
+      <c r="E123" t="str">
+        <v>Dragonborn (Draconblood; Brass)</v>
+      </c>
+      <c r="F123" t="str">
+        <v>EGW</v>
+      </c>
+      <c r="G123" t="str">
+        <v>龙裔 (龙血裔; 黄铜)</v>
+      </c>
+      <c r="H123" t="str">
+        <v>Dragonborn (Draconblood; Brass)</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="str">
+        <v>龙裔</v>
+      </c>
+      <c r="B124" t="str">
+        <v>Dragonborn</v>
+      </c>
+      <c r="C124" t="str">
+        <v>PHB</v>
+      </c>
+      <c r="D124" t="str">
+        <v>龙裔 (龙血裔; 青铜)</v>
+      </c>
+      <c r="E124" t="str">
+        <v>Dragonborn (Draconblood; Bronze)</v>
+      </c>
+      <c r="F124" t="str">
+        <v>EGW</v>
+      </c>
+      <c r="G124" t="str">
+        <v>龙裔 (龙血裔; 青铜)</v>
+      </c>
+      <c r="H124" t="str">
+        <v>Dragonborn (Draconblood; Bronze)</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="str">
+        <v>龙裔</v>
+      </c>
+      <c r="B125" t="str">
+        <v>Dragonborn</v>
+      </c>
+      <c r="C125" t="str">
+        <v>PHB</v>
+      </c>
+      <c r="D125" t="str">
+        <v>龙裔 (龙血裔; 赤铜)</v>
+      </c>
+      <c r="E125" t="str">
+        <v>Dragonborn (Draconblood; Copper)</v>
+      </c>
+      <c r="F125" t="str">
+        <v>EGW</v>
+      </c>
+      <c r="G125" t="str">
+        <v>龙裔 (龙血裔; 赤铜)</v>
+      </c>
+      <c r="H125" t="str">
+        <v>Dragonborn (Draconblood; Copper)</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="str">
+        <v>龙裔</v>
+      </c>
+      <c r="B126" t="str">
+        <v>Dragonborn</v>
+      </c>
+      <c r="C126" t="str">
+        <v>PHB</v>
+      </c>
+      <c r="D126" t="str">
+        <v>龙裔 (龙血裔; 金)</v>
+      </c>
+      <c r="E126" t="str">
+        <v>Dragonborn (Draconblood; Gold)</v>
+      </c>
+      <c r="F126" t="str">
+        <v>EGW</v>
+      </c>
+      <c r="G126" t="str">
+        <v>龙裔 (龙血裔; 金)</v>
+      </c>
+      <c r="H126" t="str">
+        <v>Dragonborn (Draconblood; Gold)</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="str">
+        <v>龙裔</v>
+      </c>
+      <c r="B127" t="str">
+        <v>Dragonborn</v>
+      </c>
+      <c r="C127" t="str">
+        <v>PHB</v>
+      </c>
+      <c r="D127" t="str">
+        <v>龙裔 (龙血裔; 绿)</v>
+      </c>
+      <c r="E127" t="str">
+        <v>Dragonborn (Draconblood; Green)</v>
+      </c>
+      <c r="F127" t="str">
+        <v>EGW</v>
+      </c>
+      <c r="G127" t="str">
+        <v>龙裔 (龙血裔; 绿)</v>
+      </c>
+      <c r="H127" t="str">
+        <v>Dragonborn (Draconblood; Green)</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="str">
+        <v>龙裔</v>
+      </c>
+      <c r="B128" t="str">
+        <v>Dragonborn</v>
+      </c>
+      <c r="C128" t="str">
+        <v>PHB</v>
+      </c>
+      <c r="D128" t="str">
+        <v>龙裔 (龙血裔; 红)</v>
+      </c>
+      <c r="E128" t="str">
+        <v>Dragonborn (Draconblood; Red)</v>
+      </c>
+      <c r="F128" t="str">
+        <v>EGW</v>
+      </c>
+      <c r="G128" t="str">
+        <v>龙裔 (龙血裔; 红)</v>
+      </c>
+      <c r="H128" t="str">
+        <v>Dragonborn (Draconblood; Red)</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="str">
+        <v>龙裔</v>
+      </c>
+      <c r="B129" t="str">
+        <v>Dragonborn</v>
+      </c>
+      <c r="C129" t="str">
+        <v>PHB</v>
+      </c>
+      <c r="D129" t="str">
+        <v>龙裔 (龙血裔; 银)</v>
+      </c>
+      <c r="E129" t="str">
+        <v>Dragonborn (Draconblood; Silver)</v>
+      </c>
+      <c r="F129" t="str">
+        <v>EGW</v>
+      </c>
+      <c r="G129" t="str">
+        <v>龙裔 (龙血裔; 银)</v>
+      </c>
+      <c r="H129" t="str">
+        <v>Dragonborn (Draconblood; Silver)</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="str">
+        <v>龙裔</v>
+      </c>
+      <c r="B130" t="str">
+        <v>Dragonborn</v>
+      </c>
+      <c r="C130" t="str">
+        <v>PHB</v>
+      </c>
+      <c r="D130" t="str">
+        <v>龙裔 (龙血裔; 白)</v>
+      </c>
+      <c r="E130" t="str">
+        <v>Dragonborn (Draconblood; White)</v>
+      </c>
+      <c r="F130" t="str">
+        <v>EGW</v>
+      </c>
+      <c r="G130" t="str">
+        <v>龙裔 (龙血裔; 白)</v>
+      </c>
+      <c r="H130" t="str">
+        <v>Dragonborn (Draconblood; White)</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="str">
+        <v>龙裔</v>
+      </c>
+      <c r="B131" t="str">
+        <v>Dragonborn</v>
+      </c>
+      <c r="C131" t="str">
+        <v>PHB</v>
+      </c>
+      <c r="D131" t="str">
+        <v>龙裔 (峡谷后; 黑)</v>
+      </c>
+      <c r="E131" t="str">
+        <v>Dragonborn (Ravenite; Black)</v>
+      </c>
+      <c r="F131" t="str">
+        <v>EGW</v>
+      </c>
+      <c r="G131" t="str">
+        <v>龙裔 (峡谷后; 黑)</v>
+      </c>
+      <c r="H131" t="str">
+        <v>Dragonborn (Ravenite; Black)</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="str">
+        <v>龙裔</v>
+      </c>
+      <c r="B132" t="str">
+        <v>Dragonborn</v>
+      </c>
+      <c r="C132" t="str">
+        <v>PHB</v>
+      </c>
+      <c r="D132" t="str">
+        <v>龙裔 (峡谷后; 蓝)</v>
+      </c>
+      <c r="E132" t="str">
+        <v>Dragonborn (Ravenite; Blue)</v>
+      </c>
+      <c r="F132" t="str">
+        <v>EGW</v>
+      </c>
+      <c r="G132" t="str">
+        <v>龙裔 (峡谷后; 蓝)</v>
+      </c>
+      <c r="H132" t="str">
+        <v>Dragonborn (Ravenite; Blue)</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="str">
+        <v>龙裔</v>
+      </c>
+      <c r="B133" t="str">
+        <v>Dragonborn</v>
+      </c>
+      <c r="C133" t="str">
+        <v>PHB</v>
+      </c>
+      <c r="D133" t="str">
+        <v>龙裔 (峡谷后; 黄铜)</v>
+      </c>
+      <c r="E133" t="str">
+        <v>Dragonborn (Ravenite; Brass)</v>
+      </c>
+      <c r="F133" t="str">
+        <v>EGW</v>
+      </c>
+      <c r="G133" t="str">
+        <v>龙裔 (峡谷后; 黄铜)</v>
+      </c>
+      <c r="H133" t="str">
+        <v>Dragonborn (Ravenite; Brass)</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="str">
+        <v>龙裔</v>
+      </c>
+      <c r="B134" t="str">
+        <v>Dragonborn</v>
+      </c>
+      <c r="C134" t="str">
+        <v>PHB</v>
+      </c>
+      <c r="D134" t="str">
+        <v>龙裔 (峡谷后; 青铜)</v>
+      </c>
+      <c r="E134" t="str">
+        <v>Dragonborn (Ravenite; Bronze)</v>
+      </c>
+      <c r="F134" t="str">
+        <v>EGW</v>
+      </c>
+      <c r="G134" t="str">
+        <v>龙裔 (峡谷后; 青铜)</v>
+      </c>
+      <c r="H134" t="str">
+        <v>Dragonborn (Ravenite; Bronze)</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="str">
+        <v>龙裔</v>
+      </c>
+      <c r="B135" t="str">
+        <v>Dragonborn</v>
+      </c>
+      <c r="C135" t="str">
+        <v>PHB</v>
+      </c>
+      <c r="D135" t="str">
+        <v>龙裔 (峡谷后; 赤铜)</v>
+      </c>
+      <c r="E135" t="str">
+        <v>Dragonborn (Ravenite; Copper)</v>
+      </c>
+      <c r="F135" t="str">
+        <v>EGW</v>
+      </c>
+      <c r="G135" t="str">
+        <v>龙裔 (峡谷后; 赤铜)</v>
+      </c>
+      <c r="H135" t="str">
+        <v>Dragonborn (Ravenite; Copper)</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="str">
+        <v>龙裔</v>
+      </c>
+      <c r="B136" t="str">
+        <v>Dragonborn</v>
+      </c>
+      <c r="C136" t="str">
+        <v>PHB</v>
+      </c>
+      <c r="D136" t="str">
+        <v>龙裔 (峡谷后; 金)</v>
+      </c>
+      <c r="E136" t="str">
+        <v>Dragonborn (Ravenite; Gold)</v>
+      </c>
+      <c r="F136" t="str">
+        <v>EGW</v>
+      </c>
+      <c r="G136" t="str">
+        <v>龙裔 (峡谷后; 金)</v>
+      </c>
+      <c r="H136" t="str">
+        <v>Dragonborn (Ravenite; Gold)</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="str">
+        <v>龙裔</v>
+      </c>
+      <c r="B137" t="str">
+        <v>Dragonborn</v>
+      </c>
+      <c r="C137" t="str">
+        <v>PHB</v>
+      </c>
+      <c r="D137" t="str">
+        <v>龙裔 (峡谷后; 绿)</v>
+      </c>
+      <c r="E137" t="str">
+        <v>Dragonborn (Ravenite; Green)</v>
+      </c>
+      <c r="F137" t="str">
+        <v>EGW</v>
+      </c>
+      <c r="G137" t="str">
+        <v>龙裔 (峡谷后; 绿)</v>
+      </c>
+      <c r="H137" t="str">
+        <v>Dragonborn (Ravenite; Green)</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="str">
+        <v>龙裔</v>
+      </c>
+      <c r="B138" t="str">
+        <v>Dragonborn</v>
+      </c>
+      <c r="C138" t="str">
+        <v>PHB</v>
+      </c>
+      <c r="D138" t="str">
+        <v>龙裔 (峡谷后; 红)</v>
+      </c>
+      <c r="E138" t="str">
+        <v>Dragonborn (Ravenite; Red)</v>
+      </c>
+      <c r="F138" t="str">
+        <v>EGW</v>
+      </c>
+      <c r="G138" t="str">
+        <v>龙裔 (峡谷后; 红)</v>
+      </c>
+      <c r="H138" t="str">
+        <v>Dragonborn (Ravenite; Red)</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="str">
+        <v>龙裔</v>
+      </c>
+      <c r="B139" t="str">
+        <v>Dragonborn</v>
+      </c>
+      <c r="C139" t="str">
+        <v>PHB</v>
+      </c>
+      <c r="D139" t="str">
+        <v>龙裔 (峡谷后; 银)</v>
+      </c>
+      <c r="E139" t="str">
+        <v>Dragonborn (Ravenite; Silver)</v>
+      </c>
+      <c r="F139" t="str">
+        <v>EGW</v>
+      </c>
+      <c r="G139" t="str">
+        <v>龙裔 (峡谷后; 银)</v>
+      </c>
+      <c r="H139" t="str">
+        <v>Dragonborn (Ravenite; Silver)</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="str">
+        <v>龙裔</v>
+      </c>
+      <c r="B140" t="str">
+        <v>Dragonborn</v>
+      </c>
+      <c r="C140" t="str">
+        <v>PHB</v>
+      </c>
+      <c r="D140" t="str">
+        <v>龙裔 (峡谷后; 白)</v>
+      </c>
+      <c r="E140" t="str">
+        <v>Dragonborn (Ravenite; White)</v>
+      </c>
+      <c r="F140" t="str">
+        <v>EGW</v>
+      </c>
+      <c r="G140" t="str">
+        <v>龙裔 (峡谷后; 白)</v>
+      </c>
+      <c r="H140" t="str">
+        <v>Dragonborn (Ravenite; White)</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H99"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H140"/>
   </ignoredErrors>
 </worksheet>
 </file>